--- a/veille-techno.xlsx
+++ b/veille-techno.xlsx
@@ -265,6 +265,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -529,14 +530,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:U121"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="69.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="74.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="121.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="66.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="66.47"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -855,61 +856,63 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="1"/>
+      <c r="B22" s="4" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="1"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="1"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
-      <c r="B23" s="4" t="n">
-        <v>46076</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="B23" s="4"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
       <c r="B24" s="7"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
       <c r="B25" s="7"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
       <c r="B27" s="7"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="7"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -921,205 +924,171 @@
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="7"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
       <c r="B34" s="7"/>
       <c r="C34" s="6"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
       <c r="B36" s="7"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
       <c r="B38" s="10"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="10"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
       <c r="B40" s="7"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
       <c r="B41" s="7"/>
-      <c r="E41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
       <c r="B42" s="10"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
       <c r="B43" s="7"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
       <c r="B44" s="7"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="D45" s="5"/>
-      <c r="E45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
       <c r="B46" s="7"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
       <c r="B47" s="7"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
       <c r="B48" s="7"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10"/>
       <c r="B49" s="4"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
       <c r="B52" s="4"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10"/>
       <c r="B55" s="7"/>
       <c r="D55" s="5"/>
-      <c r="E55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="D57" s="5"/>
-      <c r="E57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4"/>
       <c r="B59" s="7"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="D61" s="5"/>
-      <c r="E61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
@@ -1131,56 +1100,47 @@
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="D66" s="5"/>
-      <c r="E66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="D68" s="5"/>
-      <c r="E68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="6"/>
       <c r="D69" s="5"/>
-      <c r="E69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
       <c r="B70" s="4"/>
       <c r="D70" s="5"/>
-      <c r="E70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
@@ -1192,32 +1152,27 @@
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="D76" s="5"/>
-      <c r="E76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="D77" s="5"/>
-      <c r="E77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="6"/>
       <c r="D79" s="5"/>
-      <c r="E79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="D80" s="5"/>
-      <c r="E80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4"/>
@@ -1279,7 +1234,6 @@
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="4"/>
       <c r="D92" s="5"/>
-      <c r="E92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1331,8 +1285,8 @@
     <hyperlink ref="D18" r:id="rId17" display="https://www.bitget.com/fr/news/detail/12560605214946"/>
     <hyperlink ref="D19" r:id="rId18" display="https://www.phonandroid.com/la-federation-francaise-dathletisme-victime-dun-piratage-les-donnees-de-11-millions-dadherents-sont-dans-la-nature.html"/>
     <hyperlink ref="D20" r:id="rId19" display="https://francoischarron.com/securite/fraude-et-arnaques-web/-3-milliards-dadresses-courriel-compromises-et-diffusees-sur-le-dark-web/QqAoM2jyAw/"/>
-    <hyperlink ref="D21" r:id="rId20" display="https://leclaireur.fnac.com/article/658193-nouvelle-fuite-de-donnees-a-la-caf-qui-est-concerne/"/>
-    <hyperlink ref="D23" r:id="rId21" display="https://directinfo.webmanagercenter.com/2026/02/23/cybercriminalite-la-poste-tunisienne-alerte-contre-des-tentatives-de-piratage-de-cartes-de-paiement/"/>
+    <hyperlink ref="D21" r:id="rId20" display="https://leclaireur.fnac.com/article/658193-nouvelle-fuite-de-donnees-a-la-caf-qui-est-concerne/&#10;"/>
+    <hyperlink ref="D22" r:id="rId21" display="https://directinfo.webmanagercenter.com/2026/02/23/cybercriminalite-la-poste-tunisienne-alerte-contre-des-tentatives-de-piratage-de-cartes-de-paiement/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/veille-techno.xlsx
+++ b/veille-techno.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">Titre : Les hackers : Black Hat, White Hat et Grey Hat, leur rôle dans la cybersécurité </t>
   </si>
@@ -53,16 +53,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mots-clés : Police, coréenne, repère, deuxième, voleur, après</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une cyberattaque chez le prestataire de billetterie de la Citadelle de Namur : des données personnelles potentiellement concernées
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lanouvellerepublique.fr/vienne/commune/chasseneuil-du-poitou/prestataire-de-billetterie-pour-des-musees-monuments-et-parcs-de-loisirs-vivaticket-victime-d-une-cyberattaque-1773588253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mots-clés : Prestataire, billetterie, pour, musées, monuments, parcs</t>
   </si>
   <si>
     <t xml:space="preserve">Un white hat récupère 1,8 million $ après le hack de 2,3 M$ sur Foom Cash
@@ -382,12 +372,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -587,12 +577,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
-      <c r="B4" s="4" t="n">
-        <v>46094</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="6" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -601,13 +591,14 @@
       <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
-      <c r="B5" s="7" t="n">
-        <v>46091</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="4" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -616,6 +607,7 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
@@ -631,13 +623,14 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="n">
-        <v>46094</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>46093</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -646,13 +639,14 @@
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -661,9 +655,10 @@
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="4" t="n">
         <v>46093</v>
       </c>
@@ -676,11 +671,12 @@
       <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="n">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -691,6 +687,7 @@
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
@@ -706,6 +703,7 @@
       <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -721,11 +719,12 @@
       <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="n">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>38</v>
@@ -736,11 +735,12 @@
       <c r="E13" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
-      <c r="B14" s="4" t="n">
-        <v>46090</v>
+      <c r="B14" s="6" t="n">
+        <v>46088</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>41</v>
@@ -751,10 +751,11 @@
       <c r="E14" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="4" t="n">
         <v>46088</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -766,11 +767,12 @@
       <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
-      <c r="B16" s="4" t="n">
-        <v>46088</v>
+      <c r="B16" s="6" t="n">
+        <v>46091</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>47</v>
@@ -781,38 +783,41 @@
       <c r="E16" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
-      <c r="B17" s="7" t="n">
-        <v>46091</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="6" t="n">
+        <v>46092</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
-      <c r="B18" s="7" t="n">
-        <v>46092</v>
+      <c r="B18" s="6" t="n">
+        <v>46087</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
-      <c r="B19" s="7" t="n">
-        <v>46087</v>
+      <c r="B19" s="6" t="n">
+        <v>46085</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>55</v>
@@ -823,51 +828,44 @@
       <c r="E19" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
-      <c r="B20" s="7" t="n">
-        <v>46085</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="B20" s="6" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
-      <c r="B21" s="7" t="n">
-        <v>46086</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="4" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
-      <c r="B22" s="4" t="n">
-        <v>46076</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="B22" s="4"/>
+      <c r="D22" s="5"/>
       <c r="H22" s="4"/>
       <c r="I22" s="1"/>
       <c r="J22" s="5"/>
@@ -886,12 +884,12 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
-      <c r="B24" s="7"/>
+      <c r="B24" s="6"/>
       <c r="D24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
-      <c r="B25" s="7"/>
+      <c r="B25" s="6"/>
       <c r="D25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -901,7 +899,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
-      <c r="B27" s="7"/>
+      <c r="B27" s="6"/>
       <c r="D27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -911,34 +909,34 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
-      <c r="B29" s="7"/>
+      <c r="B29" s="6"/>
       <c r="D29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
-      <c r="B30" s="7"/>
+      <c r="B30" s="6"/>
       <c r="D30" s="5"/>
       <c r="E30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
+      <c r="B31" s="6"/>
       <c r="D31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
-      <c r="B32" s="7"/>
+      <c r="B32" s="6"/>
       <c r="D32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
-      <c r="B33" s="7"/>
+      <c r="B33" s="6"/>
       <c r="D33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
       <c r="D34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -948,12 +946,12 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
-      <c r="B36" s="7"/>
+      <c r="B36" s="6"/>
       <c r="D36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
       <c r="D37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -962,32 +960,32 @@
       <c r="D38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
+      <c r="A39" s="6"/>
       <c r="B39" s="10"/>
       <c r="D39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10"/>
-      <c r="B40" s="7"/>
+      <c r="B40" s="6"/>
       <c r="D40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
-      <c r="B41" s="7"/>
+      <c r="B41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
+      <c r="A42" s="6"/>
       <c r="B42" s="10"/>
       <c r="D42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10"/>
-      <c r="B43" s="7"/>
+      <c r="B43" s="6"/>
       <c r="D43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
-      <c r="B44" s="7"/>
+      <c r="B44" s="6"/>
       <c r="D44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -997,17 +995,17 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
-      <c r="B46" s="7"/>
+      <c r="B46" s="6"/>
       <c r="D46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10"/>
-      <c r="B47" s="7"/>
+      <c r="B47" s="6"/>
       <c r="D47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
-      <c r="B48" s="7"/>
+      <c r="B48" s="6"/>
       <c r="D48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1016,13 +1014,13 @@
       <c r="D49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
       <c r="D50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
       <c r="D51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1031,48 +1029,48 @@
       <c r="D52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
       <c r="D53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
       <c r="D54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10"/>
-      <c r="B55" s="7"/>
+      <c r="B55" s="6"/>
       <c r="D55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
       <c r="D56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
       <c r="D57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
       <c r="D58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4"/>
-      <c r="B59" s="7"/>
+      <c r="B59" s="6"/>
       <c r="D59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
       <c r="D60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
       <c r="D61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,50 +1079,50 @@
       <c r="D62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
       <c r="D63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
       <c r="D64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
       <c r="D65" s="5"/>
       <c r="E65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
       <c r="D66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
       <c r="D67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
       <c r="D68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="6"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="7"/>
       <c r="D69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7"/>
+      <c r="A70" s="6"/>
       <c r="B70" s="4"/>
       <c r="D70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
       <c r="D71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1133,40 +1131,40 @@
       <c r="D72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
       <c r="D73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
       <c r="D74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
       <c r="D75" s="5"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
       <c r="D76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
       <c r="D77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
       <c r="D78" s="5"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="6"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="7"/>
       <c r="D79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1217,7 +1215,7 @@
       <c r="E88" s="11"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="7"/>
+      <c r="B89" s="6"/>
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
@@ -1268,25 +1266,24 @@
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="https://www.clubic.com/actualite-604089-infomaniak-s-offre-un-expert-black-hat-et-mise-200-millions-sur-la-souverainete.html"/>
     <hyperlink ref="D3" r:id="rId2" display="https://coinedition.com/fr/la-police-sud-coreenne-repere-le-deuxieme-voleur-apres-une-perte-de-48-millions-de-dollars-du-service-des-impots-sud-coreen/"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://www.lanouvellerepublique.fr/vienne/commune/chasseneuil-du-poitou/prestataire-de-billetterie-pour-des-musees-monuments-et-parcs-de-loisirs-vivaticket-victime-d-une-cyberattaque-1773588253"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://cryptonaute.fr/white-hat-recupere-millions-foom-cash/"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://fr.businessam.be/pologne-dejoue-une-cyberattaque-contre-son-centre-de-recherche-nucleaire/"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://www.leparisien.fr/faits-divers/deux-jeunes-pirates-informatiques-arretes-apres-la-cyberattaque-contre-loffice-francais-de-limmigration-13-03-2026-Q3COVSKCZFCQFHZZMQ4AABP24E.php"/>
-    <hyperlink ref="D8" r:id="rId7" display="https://www.ouest-france.fr/high-tech/on-peut-tout-extraire-comment-des-hackers-peuvent-fouiller-dans-votre-telephone-meme-sil-est-eteint-9f7f4c06-1e05-11f1-b5d3-cf0dc99e7158"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://www.usine-digitale.fr/cybersecurite/le-recap-cyber/cyberattaques-derriere-les-annonces-de-fuites-de-donnees-beaucoup-de-bluff.W43X7XTFNBGJTMXXTALCYZSJL4.html"/>
-    <hyperlink ref="D10" r:id="rId9" display="https://tribunedelyon.fr/economie/cyberattaque-sur-la-billetterie-de-quatre-musees-lyonnais/"/>
-    <hyperlink ref="D11" r:id="rId10" display="https://www.mediaterranee.com/1022026-cyberattaque-mondiale-whatsapp-et-signal-cibles-par-des-hackers-russes.html"/>
-    <hyperlink ref="D12" r:id="rId11" display="https://www.ouest-france.fr/europe/ukraine/guerre-en-ukraine-discussion-entre-poutine-et-trump-cyberattaque-russe-le-point-sur-la-nuit-000a0332-1bdf-11f1-a3b0-65a4a3dce1a8"/>
-    <hyperlink ref="D13" r:id="rId12" display="https://www.laquotidienne.fr/une-vague-de-cyberattaques-cible-les-agences-de-voyages-via-le-systeme-ndc/"/>
-    <hyperlink ref="D14" r:id="rId13" display="https://www.usine-digitale.fr/cybersecurite/1500-medecins-victimes-169-000-dossiers-medicaux-compromis-comment-la-cyberattaque-chez-cegedim-sante-interroge-la-gouvernance-des-donnees-medicales.CL4W5RGS5JBS5O77NMVPKVWBGU.html"/>
-    <hyperlink ref="D15" r:id="rId14" display="https://www.ouest-france.fr/societe/faits-divers/en-bretagne-une-collectivite-surfacturee-pour-des-appels-a-letranger-apres-un-piratage-de-son-standard-telephonique-fe9629c8-1a07-11f1-9fa1-ca7616976f61"/>
-    <hyperlink ref="D16" r:id="rId15" display="https://www.journaldugeek.com/2026/03/07/ghost-tapping-lattaque-fantome-qui-exploite-nos-smartphones/"/>
-    <hyperlink ref="D17" r:id="rId16" display="https://www.zataz.com/decouverte-dun-espace-qui-qui-flirte-avec-lombre-quand-la-veille-vulnerabilites-devient-un-manuel-dattaque/"/>
-    <hyperlink ref="D18" r:id="rId17" display="https://www.bitget.com/fr/news/detail/12560605214946"/>
-    <hyperlink ref="D19" r:id="rId18" display="https://www.phonandroid.com/la-federation-francaise-dathletisme-victime-dun-piratage-les-donnees-de-11-millions-dadherents-sont-dans-la-nature.html"/>
-    <hyperlink ref="D20" r:id="rId19" display="https://francoischarron.com/securite/fraude-et-arnaques-web/-3-milliards-dadresses-courriel-compromises-et-diffusees-sur-le-dark-web/QqAoM2jyAw/"/>
-    <hyperlink ref="D21" r:id="rId20" display="https://leclaireur.fnac.com/article/658193-nouvelle-fuite-de-donnees-a-la-caf-qui-est-concerne/&#10;"/>
-    <hyperlink ref="D22" r:id="rId21" display="https://directinfo.webmanagercenter.com/2026/02/23/cybercriminalite-la-poste-tunisienne-alerte-contre-des-tentatives-de-piratage-de-cartes-de-paiement/"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://cryptonaute.fr/white-hat-recupere-millions-foom-cash/"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://fr.businessam.be/pologne-dejoue-une-cyberattaque-contre-son-centre-de-recherche-nucleaire/"/>
+    <hyperlink ref="D6" r:id="rId5" display="https://www.leparisien.fr/faits-divers/deux-jeunes-pirates-informatiques-arretes-apres-la-cyberattaque-contre-loffice-francais-de-limmigration-13-03-2026-Q3COVSKCZFCQFHZZMQ4AABP24E.php"/>
+    <hyperlink ref="D7" r:id="rId6" display="https://www.ouest-france.fr/high-tech/on-peut-tout-extraire-comment-des-hackers-peuvent-fouiller-dans-votre-telephone-meme-sil-est-eteint-9f7f4c06-1e05-11f1-b5d3-cf0dc99e7158"/>
+    <hyperlink ref="D8" r:id="rId7" display="https://www.usine-digitale.fr/cybersecurite/le-recap-cyber/cyberattaques-derriere-les-annonces-de-fuites-de-donnees-beaucoup-de-bluff.W43X7XTFNBGJTMXXTALCYZSJL4.html"/>
+    <hyperlink ref="D9" r:id="rId8" display="https://tribunedelyon.fr/economie/cyberattaque-sur-la-billetterie-de-quatre-musees-lyonnais/"/>
+    <hyperlink ref="D10" r:id="rId9" display="https://www.mediaterranee.com/1022026-cyberattaque-mondiale-whatsapp-et-signal-cibles-par-des-hackers-russes.html"/>
+    <hyperlink ref="D11" r:id="rId10" display="https://www.ouest-france.fr/europe/ukraine/guerre-en-ukraine-discussion-entre-poutine-et-trump-cyberattaque-russe-le-point-sur-la-nuit-000a0332-1bdf-11f1-a3b0-65a4a3dce1a8"/>
+    <hyperlink ref="D12" r:id="rId11" display="https://www.laquotidienne.fr/une-vague-de-cyberattaques-cible-les-agences-de-voyages-via-le-systeme-ndc/"/>
+    <hyperlink ref="D13" r:id="rId12" display="https://www.usine-digitale.fr/cybersecurite/1500-medecins-victimes-169-000-dossiers-medicaux-compromis-comment-la-cyberattaque-chez-cegedim-sante-interroge-la-gouvernance-des-donnees-medicales.CL4W5RGS5JBS5O77NMVPKVWBGU.html"/>
+    <hyperlink ref="D14" r:id="rId13" display="https://www.ouest-france.fr/societe/faits-divers/en-bretagne-une-collectivite-surfacturee-pour-des-appels-a-letranger-apres-un-piratage-de-son-standard-telephonique-fe9629c8-1a07-11f1-9fa1-ca7616976f61"/>
+    <hyperlink ref="D15" r:id="rId14" display="https://www.journaldugeek.com/2026/03/07/ghost-tapping-lattaque-fantome-qui-exploite-nos-smartphones/"/>
+    <hyperlink ref="D16" r:id="rId15" display="https://www.zataz.com/decouverte-dun-espace-qui-qui-flirte-avec-lombre-quand-la-veille-vulnerabilites-devient-un-manuel-dattaque/"/>
+    <hyperlink ref="D17" r:id="rId16" display="https://www.bitget.com/fr/news/detail/12560605214946"/>
+    <hyperlink ref="D18" r:id="rId17" display="https://www.phonandroid.com/la-federation-francaise-dathletisme-victime-dun-piratage-les-donnees-de-11-millions-dadherents-sont-dans-la-nature.html"/>
+    <hyperlink ref="D19" r:id="rId18" display="https://francoischarron.com/securite/fraude-et-arnaques-web/-3-milliards-dadresses-courriel-compromises-et-diffusees-sur-le-dark-web/QqAoM2jyAw/"/>
+    <hyperlink ref="D20" r:id="rId19" display="https://leclaireur.fnac.com/article/658193-nouvelle-fuite-de-donnees-a-la-caf-qui-est-concerne/&#10;"/>
+    <hyperlink ref="D21" r:id="rId20" display="https://directinfo.webmanagercenter.com/2026/02/23/cybercriminalite-la-poste-tunisienne-alerte-contre-des-tentatives-de-piratage-de-cartes-de-paiement/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
